--- a/results/tables/03_env_driven_taxa_clusters/table6_lda_classification_report.xlsx
+++ b/results/tables/03_env_driven_taxa_clusters/table6_lda_classification_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,16 +457,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="D2" t="n">
-        <v>0.77</v>
+        <v>0.89</v>
       </c>
       <c r="E2" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -476,104 +476,123 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="C3" t="n">
-        <v>0.64</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="E3" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Cluster 2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E5" t="n">
-        <v>52</v>
-      </c>
+      <c r="A5" s="1" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Macro avg</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.72</v>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>0.72</v>
+        <v>0.83</v>
       </c>
       <c r="E6" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Weighted avg</t>
+          <t>Macro avg</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="C7" t="n">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="D7" t="n">
         <v>0.73</v>
       </c>
       <c r="E7" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Weighted avg</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E8" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Note: Overall Accuracy = 0.7308; Number of sites = 52.0</t>
-        </is>
-      </c>
+      <c r="A9" s="1" t="inlineStr"/>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Note: Overall Accuracy = 0.8261; Number of sites = 46.0</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
